--- a/acceuil/ig/cm-v3-administrative-gender.xlsx
+++ b/acceuil/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T14:04:47+00:00</t>
+    <t>2026-03-26T12:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/acceuil/ig/cm-v3-administrative-gender.xlsx
+++ b/acceuil/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T12:27:46+00:00</t>
+    <t>2026-03-26T13:32:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/acceuil/ig/cm-v3-administrative-gender.xlsx
+++ b/acceuil/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T13:32:38+00:00</t>
+    <t>2026-03-26T17:44:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/acceuil/ig/cm-v3-administrative-gender.xlsx
+++ b/acceuil/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T17:44:42+00:00</t>
+    <t>2026-03-27T10:46:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/acceuil/ig/cm-v3-administrative-gender.xlsx
+++ b/acceuil/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:46:37+00:00</t>
+    <t>2026-03-27T10:51:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/acceuil/ig/cm-v3-administrative-gender.xlsx
+++ b/acceuil/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:51:24+00:00</t>
+    <t>2026-03-27T11:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
